--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E454AF3-0505-4C12-B59F-8CF7613F3B54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48EB80EC-7E1F-4C8F-A1D1-E2E71AAED7FD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1FFDDC7-67D9-4FDA-965D-1D530F33E51C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09DA9F89-BC4F-4834-BCB6-B6FD3796E942}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{039E9A96-0F3E-4EAE-ADA7-36472D9C6A9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80C556EE-CEC7-4671-B01C-30A055D735BE}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48EB80EC-7E1F-4C8F-A1D1-E2E71AAED7FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D5797CC-144E-45F4-9C04-605E8C23B7C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09DA9F89-BC4F-4834-BCB6-B6FD3796E942}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F9BBFAF-F615-4BAB-A9FC-0B44A8B19E37}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80C556EE-CEC7-4671-B01C-30A055D735BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{565C6BAD-3B94-4B09-BFE7-3FAE54B791CD}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D5797CC-144E-45F4-9C04-605E8C23B7C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D41DE173-AC61-402D-BD53-D5FD8D9463EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F9BBFAF-F615-4BAB-A9FC-0B44A8B19E37}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{863EF738-97FB-4081-B4EC-11D7C7857B6A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{565C6BAD-3B94-4B09-BFE7-3FAE54B791CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6903B17D-7DCE-423A-921F-98FA3E3BF4A1}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1332,22 +1332,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48EB80EC-7E1F-4C8F-A1D1-E2E71AAED7FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B24E404-3E8D-4A2D-BCFD-EDD6CD3CDBF7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09DA9F89-BC4F-4834-BCB6-B6FD3796E942}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA0FB76-F430-4E3E-B4A1-11FAD12C24DB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80C556EE-CEC7-4671-B01C-30A055D735BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0AE6DCA-7DD7-4195-9ED3-E2F92E5DA0EE}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1332,22 +1332,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D41DE173-AC61-402D-BD53-D5FD8D9463EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ED5CDD6-A752-4924-80B9-64A021868ABF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{863EF738-97FB-4081-B4EC-11D7C7857B6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E31CDEB-FA88-4A30-B941-F13BDAA23FEC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6903B17D-7DCE-423A-921F-98FA3E3BF4A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E096C0-3A35-4E84-9EF4-22828B9018BD}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ED5CDD6-A752-4924-80B9-64A021868ABF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3050A28-032C-4E22-A9B0-C16D34AA7493}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E31CDEB-FA88-4A30-B941-F13BDAA23FEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60985C7F-415A-4230-BD85-07D7D57A2BC3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E096C0-3A35-4E84-9EF4-22828B9018BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B9A380-957F-4FF4-AE9C-90C37A72943B}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3050A28-032C-4E22-A9B0-C16D34AA7493}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{197F3780-D27C-4521-9216-AC4B967B59D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60985C7F-415A-4230-BD85-07D7D57A2BC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{842D05A6-F5C9-457A-A0B4-DE7FE2570D43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B9A380-957F-4FF4-AE9C-90C37A72943B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF43C2D6-731F-48A5-A5ED-D808F91A1F54}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{197F3780-D27C-4521-9216-AC4B967B59D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981CD945-A524-4A9B-A07C-73E958C87361}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{842D05A6-F5C9-457A-A0B4-DE7FE2570D43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C33246D-7B51-4333-8FC1-03A112B74107}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF43C2D6-731F-48A5-A5ED-D808F91A1F54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD1561D6-CE73-4332-914F-366F70B2C209}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981CD945-A524-4A9B-A07C-73E958C87361}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6F867A-513D-48F6-8761-D63005CB3078}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C33246D-7B51-4333-8FC1-03A112B74107}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74F38E4E-3CDB-421D-B72D-3906358317CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD1561D6-CE73-4332-914F-366F70B2C209}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B0BC24-E669-45FF-B4A7-78346918445E}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6F867A-513D-48F6-8761-D63005CB3078}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8684B4B4-172E-4E76-A047-FD722E8A6FE1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74F38E4E-3CDB-421D-B72D-3906358317CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932110DF-F1FF-4356-80A7-E1046CE88EF5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B0BC24-E669-45FF-B4A7-78346918445E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFFBFE1C-11F7-4C63-B517-0D0710C89EF1}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8684B4B4-172E-4E76-A047-FD722E8A6FE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD579EA6-85DE-4259-9A1F-AC3A24EE2CE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932110DF-F1FF-4356-80A7-E1046CE88EF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFDB0229-3908-4AC4-8B1A-75DE2097DA6A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFFBFE1C-11F7-4C63-B517-0D0710C89EF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D34FD2FD-E323-4A1D-B6DA-F7AB7AD80BD7}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD579EA6-85DE-4259-9A1F-AC3A24EE2CE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED51293C-757A-4B62-B8A7-FE0CB3B32499}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFDB0229-3908-4AC4-8B1A-75DE2097DA6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADD33DAF-F1DE-4DA9-B1CA-ED4D0D6DA745}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D34FD2FD-E323-4A1D-B6DA-F7AB7AD80BD7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93C2E38-C6F2-4FE7-8DB6-8BDC30B48B9D}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED51293C-757A-4B62-B8A7-FE0CB3B32499}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07BF9C39-86C1-4447-95EA-6D6E811C8649}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADD33DAF-F1DE-4DA9-B1CA-ED4D0D6DA745}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A44605B8-5B9E-4E56-B336-9D4FC3A6437A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93C2E38-C6F2-4FE7-8DB6-8BDC30B48B9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{967047C2-1766-41E6-8B68-F962C07DDAE0}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07BF9C39-86C1-4447-95EA-6D6E811C8649}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD98A2D0-742D-4782-9C1D-267E651F94E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A44605B8-5B9E-4E56-B336-9D4FC3A6437A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A155270-F998-46B9-9CA3-D817C21DBC36}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{967047C2-1766-41E6-8B68-F962C07DDAE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{399A9574-9402-48C4-8030-45DF8BE7F13C}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD98A2D0-742D-4782-9C1D-267E651F94E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A77A7E-19E5-4C88-8967-FAC6C9C58EF6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A155270-F998-46B9-9CA3-D817C21DBC36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B659E1D5-2B58-4150-A57E-79128D1E7FBA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{399A9574-9402-48C4-8030-45DF8BE7F13C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0226A7A6-FE91-444A-9531-54B07C657455}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A77A7E-19E5-4C88-8967-FAC6C9C58EF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB8CDF0D-8730-4A21-9607-7E0C35E25D68}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B659E1D5-2B58-4150-A57E-79128D1E7FBA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8C9E343-1FFA-4429-8A56-A9F2A22BD8E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0226A7A6-FE91-444A-9531-54B07C657455}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{076EF526-DACA-49A4-9602-328BE5CF243E}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB8CDF0D-8730-4A21-9607-7E0C35E25D68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A63F7B-7D05-4F3B-A8E5-1EE99BF1D61F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8C9E343-1FFA-4429-8A56-A9F2A22BD8E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0029B61-5314-4DA8-9ADA-23934F6A4A67}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{076EF526-DACA-49A4-9602-328BE5CF243E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FA72E8-0488-4C75-89C5-79F4C6B1E34A}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A63F7B-7D05-4F3B-A8E5-1EE99BF1D61F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{507D1A91-91B9-4D85-97F3-E337AE479126}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0029B61-5314-4DA8-9ADA-23934F6A4A67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86240BE6-76CC-4934-84A1-2A4AB8F7514E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FA72E8-0488-4C75-89C5-79F4C6B1E34A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F43D24E-AD85-4DF5-B718-1308967C3714}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{507D1A91-91B9-4D85-97F3-E337AE479126}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1FFF0F-1757-436E-8B1E-95252E86630D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86240BE6-76CC-4934-84A1-2A4AB8F7514E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8116AB1F-F812-4A10-AF88-45800D239F66}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F43D24E-AD85-4DF5-B718-1308967C3714}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE4B63B1-F8F0-42E5-95C0-3C958849DB01}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1FFF0F-1757-436E-8B1E-95252E86630D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BD4D5A1-10C4-4608-897D-C4E4F9C5A425}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8116AB1F-F812-4A10-AF88-45800D239F66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D15080BF-9934-471D-8A48-68326DDB50CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE4B63B1-F8F0-42E5-95C0-3C958849DB01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B28D688-2111-4923-9B6F-2A3AED1CE277}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BD4D5A1-10C4-4608-897D-C4E4F9C5A425}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319A5E39-DB16-4819-A925-59B1A68FA670}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D15080BF-9934-471D-8A48-68326DDB50CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D3A1E98-623C-433E-8193-6E0FE06A88C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B28D688-2111-4923-9B6F-2A3AED1CE277}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26EB20DB-6DB3-45BD-B5E6-E5F760D76303}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319A5E39-DB16-4819-A925-59B1A68FA670}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D149692D-2F09-4B63-A880-C8D1ADEDC3DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D3A1E98-623C-433E-8193-6E0FE06A88C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD5E741A-95ED-44B8-B941-8B798847B6E1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26EB20DB-6DB3-45BD-B5E6-E5F760D76303}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83951DC4-9BB4-4904-8163-9CABA636B321}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D149692D-2F09-4B63-A880-C8D1ADEDC3DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67BDF9A-CFA9-49E8-AB88-24E078D6FC1A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD5E741A-95ED-44B8-B941-8B798847B6E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E21640F8-FC1A-4B54-8FCA-B4053483E60A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83951DC4-9BB4-4904-8163-9CABA636B321}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D9D96D8-AB5C-4F0A-A2EF-AB17F1A1AFFC}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67BDF9A-CFA9-49E8-AB88-24E078D6FC1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F5DEF92-44C9-48E9-9B8F-87CCCEA1D21B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E21640F8-FC1A-4B54-8FCA-B4053483E60A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FECA727-96D5-4AB2-86AF-E50B1734784A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D9D96D8-AB5C-4F0A-A2EF-AB17F1A1AFFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AA92F7-7192-4533-A14B-BCD86CCF2F6E}"/>
 </file>